--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103857</t>
+    <t>20250611134353</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:57+01:00</t>
+    <t>2025-06-11T13:43:53+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134353</t>
+    <t>20250616134739</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:53+01:00</t>
+    <t>2025-06-16T13:47:39+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134739</t>
+    <t>20250624152100</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:39+01:00</t>
+    <t>2025-06-24T15:21:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152100</t>
+    <t>20251216141838</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:00+01:00</t>
+    <t>2025-12-16T14:18:38+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,6 +121,24 @@
   </si>
   <si>
     <t>Prise en charge infirmier du diabète insulinotraité</t>
+  </si>
+  <si>
+    <t>MED-1322</t>
+  </si>
+  <si>
+    <t>Intervention d'un aide médico-psychologique</t>
+  </si>
+  <si>
+    <t>MED-1323</t>
+  </si>
+  <si>
+    <t>Intervention d'un accompagnant éducatif et social</t>
+  </si>
+  <si>
+    <t>MED-1324</t>
+  </si>
+  <si>
+    <t>Intervention d'un infirmier d'un centre de santé infirmier</t>
   </si>
   <si>
     <t/>
@@ -385,7 +403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -445,15 +463,39 @@
         <v>36</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>38</v>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141838</t>
+    <t>20260220142104</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:38+01:00</t>
+    <t>2026-02-20T14:21:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142104</t>
+    <t>20260311144903</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:04+01:00</t>
+    <t>2026-03-11T14:49:03+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144903</t>
+    <t>20260420150250</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:03+01:00</t>
+    <t>2026-04-20T15:02:50+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
+++ b/ig/DM_FINESS_New/ValueSet-jdv-type-evenement-ssiad-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260619134042</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-06-19T13:40:42+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
